--- a/results/phi4_14b/comparison_GoTPlainLLM/GoTPlainLLM_costs.xlsx
+++ b/results/phi4_14b/comparison_GoTPlainLLM/GoTPlainLLM_costs.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.003021955490112305</v>
+        <v>22.12478852272034</v>
       </c>
       <c r="B2" t="n">
-        <v>1122.52734375</v>
+        <v>1125.8359375</v>
       </c>
       <c r="C2" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -490,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003018617630004883</v>
+        <v>22.12478542327881</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -498,16 +498,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.001966238021850586</v>
+        <v>19.10640835762024</v>
       </c>
       <c r="B3" t="n">
-        <v>1122.53515625</v>
+        <v>1125.9140625</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001963376998901367</v>
+        <v>19.10640573501587</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -524,16 +524,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.002119302749633789</v>
+        <v>17.32344770431519</v>
       </c>
       <c r="B4" t="n">
-        <v>1122.53515625</v>
+        <v>1125.953125</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -542,7 +542,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002118110656738281</v>
+        <v>17.32344579696655</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -550,16 +550,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001869916915893555</v>
+        <v>20.01042413711548</v>
       </c>
       <c r="B5" t="n">
-        <v>1122.53515625</v>
+        <v>1127.4765625</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001868486404418945</v>
+        <v>20.01042199134827</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -576,16 +576,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.002080678939819336</v>
+        <v>21.75261282920837</v>
       </c>
       <c r="B6" t="n">
-        <v>1122.53515625</v>
+        <v>1127.55078125</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>11.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002079486846923828</v>
+        <v>21.75261068344116</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -602,16 +602,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.002376794815063477</v>
+        <v>31.42953681945801</v>
       </c>
       <c r="B7" t="n">
-        <v>1122.640625</v>
+        <v>1127.90234375</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002375364303588867</v>
+        <v>31.4295346736908</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -628,16 +628,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002924680709838867</v>
+        <v>29.44839692115784</v>
       </c>
       <c r="B8" t="n">
-        <v>1122.66796875</v>
+        <v>1127.90234375</v>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002910852432250977</v>
+        <v>29.44839525222778</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -654,16 +654,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.001907587051391602</v>
+        <v>29.57351756095886</v>
       </c>
       <c r="B9" t="n">
-        <v>1122.66796875</v>
+        <v>1127.90234375</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001906633377075195</v>
+        <v>29.57351541519165</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.002264976501464844</v>
+        <v>26.87655830383301</v>
       </c>
       <c r="B10" t="n">
-        <v>1122.66796875</v>
+        <v>1127.90234375</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>11.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002264022827148438</v>
+        <v>26.8765561580658</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -706,16 +706,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.00187373161315918</v>
+        <v>28.06247925758362</v>
       </c>
       <c r="B11" t="n">
-        <v>1122.66796875</v>
+        <v>1127.9375</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001872539520263672</v>
+        <v>28.06247735023499</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -732,16 +732,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.002344369888305664</v>
+        <v>26.51732444763184</v>
       </c>
       <c r="B12" t="n">
-        <v>1122.66796875</v>
+        <v>1127.953125</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002343416213989258</v>
+        <v>26.51732277870178</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -758,16 +758,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.002075910568237305</v>
+        <v>22.90320491790771</v>
       </c>
       <c r="B13" t="n">
-        <v>1122.66796875</v>
+        <v>1127.953125</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>11.6</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002074480056762695</v>
+        <v>22.90320301055908</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -784,16 +784,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002100467681884766</v>
+        <v>25.28776860237122</v>
       </c>
       <c r="B14" t="n">
-        <v>1122.66796875</v>
+        <v>1127.953125</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002099275588989258</v>
+        <v>25.28776669502258</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -810,16 +810,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.002120256423950195</v>
+        <v>20.3046600818634</v>
       </c>
       <c r="B15" t="n">
-        <v>1122.66796875</v>
+        <v>1127.953125</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002119064331054688</v>
+        <v>20.30465817451477</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -836,16 +836,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.001978874206542969</v>
+        <v>19.41476559638977</v>
       </c>
       <c r="B16" t="n">
-        <v>1122.66796875</v>
+        <v>1127.95703125</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001977920532226562</v>
+        <v>19.41476392745972</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,16 +862,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.002335071563720703</v>
+        <v>21.44692516326904</v>
       </c>
       <c r="B17" t="n">
-        <v>1122.671875</v>
+        <v>1127.95703125</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002333641052246094</v>
+        <v>21.44692325592041</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -888,16 +888,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.001950502395629883</v>
+        <v>23.94958305358887</v>
       </c>
       <c r="B18" t="n">
-        <v>1122.6796875</v>
+        <v>1127.95703125</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>11.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001949548721313477</v>
+        <v>23.94958162307739</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -914,16 +914,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.002282619476318359</v>
+        <v>23.09705519676208</v>
       </c>
       <c r="B19" t="n">
-        <v>1122.703125</v>
+        <v>1127.95703125</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.002281427383422852</v>
+        <v>23.09705352783203</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -940,16 +940,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.002015590667724609</v>
+        <v>22.91807460784912</v>
       </c>
       <c r="B20" t="n">
-        <v>1122.70703125</v>
+        <v>1127.98046875</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.002014636993408203</v>
+        <v>22.91807198524475</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.003462791442871094</v>
+        <v>39.67655372619629</v>
       </c>
       <c r="B21" t="n">
-        <v>1122.84765625</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003460884094238281</v>
+        <v>39.67655181884766</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -992,16 +992,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.002453804016113281</v>
+        <v>32.27557349205017</v>
       </c>
       <c r="B22" t="n">
-        <v>1122.8515625</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002452373504638672</v>
+        <v>32.27557182312012</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.002390623092651367</v>
+        <v>32.10565423965454</v>
       </c>
       <c r="B23" t="n">
-        <v>1122.85546875</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>10.6</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002389192581176758</v>
+        <v>32.10565137863159</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1044,16 +1044,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.001929044723510742</v>
+        <v>19.40041732788086</v>
       </c>
       <c r="B24" t="n">
-        <v>1122.85546875</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001927614212036133</v>
+        <v>19.40041542053223</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1070,16 +1070,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.002121925354003906</v>
+        <v>18.13336539268494</v>
       </c>
       <c r="B25" t="n">
-        <v>1122.85546875</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002120494842529297</v>
+        <v>18.13336372375488</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1096,16 +1096,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.001860857009887695</v>
+        <v>19.86343383789062</v>
       </c>
       <c r="B26" t="n">
-        <v>1122.85546875</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001859664916992188</v>
+        <v>19.86343216896057</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1122,16 +1122,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.002106189727783203</v>
+        <v>18.10218620300293</v>
       </c>
       <c r="B27" t="n">
-        <v>1122.85546875</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.002104759216308594</v>
+        <v>18.10218143463135</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1148,16 +1148,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.001869440078735352</v>
+        <v>18.35174608230591</v>
       </c>
       <c r="B28" t="n">
-        <v>1122.85546875</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001868009567260742</v>
+        <v>18.3517439365387</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.002075672149658203</v>
+        <v>19.92830324172974</v>
       </c>
       <c r="B29" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002074480056762695</v>
+        <v>19.92830109596252</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.002249240875244141</v>
+        <v>19.22996735572815</v>
       </c>
       <c r="B30" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002248048782348633</v>
+        <v>19.22996592521667</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1226,16 +1226,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.001905918121337891</v>
+        <v>18.89662933349609</v>
       </c>
       <c r="B31" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C31" t="n">
-        <v>33.3</v>
+        <v>10.7</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.001904964447021484</v>
+        <v>18.89662766456604</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.002118587493896484</v>
+        <v>19.64923572540283</v>
       </c>
       <c r="B32" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.002117395401000977</v>
+        <v>19.64923357963562</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.002054452896118164</v>
+        <v>22.60587668418884</v>
       </c>
       <c r="B33" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002053260803222656</v>
+        <v>22.60587501525879</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1304,16 +1304,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.002185583114624023</v>
+        <v>22.19046759605408</v>
       </c>
       <c r="B34" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C34" t="n">
-        <v>25</v>
+        <v>10.8</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002184629440307617</v>
+        <v>22.1904661655426</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1330,16 +1330,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.001955747604370117</v>
+        <v>19.71259593963623</v>
       </c>
       <c r="B35" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C35" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.001954793930053711</v>
+        <v>19.71259379386902</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1356,16 +1356,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.002138137817382812</v>
+        <v>19.07508730888367</v>
       </c>
       <c r="B36" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002137184143066406</v>
+        <v>19.07508492469788</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.00200963020324707</v>
+        <v>26.74604058265686</v>
       </c>
       <c r="B37" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002008676528930664</v>
+        <v>26.74603891372681</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1408,16 +1408,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.002190589904785156</v>
+        <v>22.3070924282074</v>
       </c>
       <c r="B38" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00218963623046875</v>
+        <v>22.30709004402161</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.05113697052001953</v>
+        <v>19.89927005767822</v>
       </c>
       <c r="B39" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0511329174041748</v>
+        <v>19.89926767349243</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1460,16 +1460,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.002626180648803711</v>
+        <v>19.04356861114502</v>
       </c>
       <c r="B40" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>10.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.002624750137329102</v>
+        <v>19.04356694221497</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1486,16 +1486,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.00193476676940918</v>
+        <v>22.51703143119812</v>
       </c>
       <c r="B41" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>11.4</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001933813095092773</v>
+        <v>22.51702928543091</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.002156734466552734</v>
+        <v>20.88469409942627</v>
       </c>
       <c r="B42" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.002155303955078125</v>
+        <v>20.88469219207764</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1538,16 +1538,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.002086877822875977</v>
+        <v>22.19956421852112</v>
       </c>
       <c r="B43" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.002085208892822266</v>
+        <v>22.19956254959106</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1564,16 +1564,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.002296924591064453</v>
+        <v>23.71668314933777</v>
       </c>
       <c r="B44" t="n">
-        <v>1122.859375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.002295732498168945</v>
+        <v>23.7166805267334</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1590,16 +1590,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.002425193786621094</v>
+        <v>30.68054127693176</v>
       </c>
       <c r="B45" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002423524856567383</v>
+        <v>30.68053936958313</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.002283334732055664</v>
+        <v>28.15051794052124</v>
       </c>
       <c r="B46" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>11.8</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.002282142639160156</v>
+        <v>28.15051627159119</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1642,16 +1642,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.002351284027099609</v>
+        <v>27.06231689453125</v>
       </c>
       <c r="B47" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002350330352783203</v>
+        <v>27.0623152256012</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1668,16 +1668,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.001970052719116211</v>
+        <v>20.33850884437561</v>
       </c>
       <c r="B48" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001969099044799805</v>
+        <v>20.33850693702698</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.002166032791137695</v>
+        <v>22.48460125923157</v>
       </c>
       <c r="B49" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>11.8</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.002164602279663086</v>
+        <v>22.48459911346436</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1720,16 +1720,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.001978635787963867</v>
+        <v>22.73816633224487</v>
       </c>
       <c r="B50" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>11.3</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.001977205276489258</v>
+        <v>22.73816418647766</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1746,16 +1746,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.002255439758300781</v>
+        <v>26.77148342132568</v>
       </c>
       <c r="B51" t="n">
-        <v>1122.86328125</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.002254486083984375</v>
+        <v>26.77148079872131</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.002103090286254883</v>
+        <v>23.46485590934753</v>
       </c>
       <c r="B52" t="n">
-        <v>1122.87109375</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.002101421356201172</v>
+        <v>23.46485304832458</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1798,16 +1798,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.002568721771240234</v>
+        <v>27.59025812149048</v>
       </c>
       <c r="B53" t="n">
-        <v>1122.90625</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.002567291259765625</v>
+        <v>27.59025597572327</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1824,16 +1824,16 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.002014398574829102</v>
+        <v>26.47705173492432</v>
       </c>
       <c r="B54" t="n">
-        <v>1122.90625</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C54" t="n">
-        <v>33.3</v>
+        <v>11.3</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.002013683319091797</v>
+        <v>26.47704982757568</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1850,16 +1850,16 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.0021820068359375</v>
+        <v>23.25298380851746</v>
       </c>
       <c r="B55" t="n">
-        <v>1122.91015625</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.002180814743041992</v>
+        <v>23.25298190116882</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1876,16 +1876,16 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.001950263977050781</v>
+        <v>21.16882419586182</v>
       </c>
       <c r="B56" t="n">
-        <v>1122.91015625</v>
+        <v>1128.32421875</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.001949548721313477</v>
+        <v>21.16882228851318</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1902,16 +1902,16 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.002827644348144531</v>
+        <v>32.27656555175781</v>
       </c>
       <c r="B57" t="n">
-        <v>1122.9296875</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C57" t="n">
-        <v>20</v>
+        <v>11.2</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.002826213836669922</v>
+        <v>32.2765634059906</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -1928,16 +1928,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.002401113510131836</v>
+        <v>19.19828152656555</v>
       </c>
       <c r="B58" t="n">
-        <v>1122.9375</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.002399444580078125</v>
+        <v>19.19827938079834</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.002303361892700195</v>
+        <v>25.09474587440491</v>
       </c>
       <c r="B59" t="n">
-        <v>1122.9375</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.002301692962646484</v>
+        <v>25.09474396705627</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -1980,16 +1980,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.002183198928833008</v>
+        <v>27.59090447425842</v>
       </c>
       <c r="B60" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.002181768417358398</v>
+        <v>27.59090232849121</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.002161502838134766</v>
+        <v>24.68773412704468</v>
       </c>
       <c r="B61" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C61" t="n">
-        <v>25</v>
+        <v>11.2</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.002160310745239258</v>
+        <v>24.68773198127747</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.001862525939941406</v>
+        <v>18.8063759803772</v>
       </c>
       <c r="B62" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.001861572265625</v>
+        <v>18.80637407302856</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2058,16 +2058,16 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.002123355865478516</v>
+        <v>20.03243947029114</v>
       </c>
       <c r="B63" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.002121925354003906</v>
+        <v>20.03243780136108</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2084,16 +2084,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.002099990844726562</v>
+        <v>19.39385914802551</v>
       </c>
       <c r="B64" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.002098560333251953</v>
+        <v>19.39385771751404</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.001873016357421875</v>
+        <v>19.84823608398438</v>
       </c>
       <c r="B65" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.001872062683105469</v>
+        <v>19.84823441505432</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.002179861068725586</v>
+        <v>19.46893239021301</v>
       </c>
       <c r="B66" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C66" t="n">
-        <v>25</v>
+        <v>10.7</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00217890739440918</v>
+        <v>19.46893072128296</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.001979827880859375</v>
+        <v>23.98936676979065</v>
       </c>
       <c r="B67" t="n">
-        <v>1122.95703125</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.001978874206542969</v>
+        <v>23.98936486244202</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2188,16 +2188,16 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.0025177001953125</v>
+        <v>31.64771699905396</v>
       </c>
       <c r="B68" t="n">
-        <v>1122.97265625</v>
+        <v>1128.37109375</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.002516746520996094</v>
+        <v>31.64771461486816</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
